--- a/ISA/vaa_out/old/vaa_composite_report_2026-01.xlsx
+++ b/ISA/vaa_out/old/vaa_composite_report_2026-01.xlsx
@@ -487,8 +487,8 @@
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
@@ -640,22 +640,22 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0151</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.0175</v>
+        <v>0.0248</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.1236</v>
+        <v>0.1317</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.139</v>
+        <v>0.1472</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>988260.0038560554</v>
+        <v>995358.3921514153</v>
       </c>
       <c r="O3" s="5" t="n">
         <v>980539.5859341547</v>
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0506</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.0068</v>
+        <v>0.0365</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.1609</v>
+        <v>0.1952</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.2112</v>
+        <v>0.247</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.39</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>2729.699788491532</v>
+        <v>2810.375128736922</v>
       </c>
       <c r="O4" s="5" t="n">
         <v>2675.069603186024</v>
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.0342</v>
+        <v>0.08439999999999999</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.0331</v>
+        <v>0.0833</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.204</v>
+        <v>0.2625</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.321</v>
+        <v>0.3851</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.27</v>
+        <v>2.26</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>81355.65915655205</v>
+        <v>85306.53277827147</v>
       </c>
       <c r="O5" s="5" t="n">
         <v>78668.05665352475</v>
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0067</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.0089</v>
+        <v>0.0098</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.0525</v>
+        <v>0.0535</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0287</v>
+        <v>0.0296</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>144441.0064047547</v>
+        <v>144574.8619031738</v>
       </c>
       <c r="O6" s="5" t="n">
         <v>143618.4502645293</v>
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.0058</v>
+        <v>0.0103</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.0061</v>
+        <v>0.0106</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.0496</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.0286</v>
+        <v>0.0332</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>159355.2532565184</v>
+        <v>160070.6928998046</v>
       </c>
       <c r="O7" s="5" t="n">
         <v>158443.3101767823</v>
@@ -1000,22 +1000,22 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.0052</v>
+        <v>0.0022</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.0525</v>
+        <v>0.0493</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0364</v>
+        <v>0.0333</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>138987.4048265014</v>
+        <v>138567.1508723143</v>
       </c>
       <c r="O8" s="5" t="n">
         <v>138269.4341525026</v>
@@ -1072,22 +1072,22 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0046</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0144</v>
+        <v>0.0124</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.0104</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>119863.6160416137</v>
+        <v>119634.2119427733</v>
       </c>
       <c r="O9" s="5" t="n">
         <v>119087.7085919464</v>
@@ -1123,7 +1123,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="10"/>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>988260.0038560554</v>
+        <v>995358.3921514153</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>980539.5859341547</v>
@@ -1266,16 +1266,16 @@
       </c>
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0151</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.0175</v>
+        <v>0.0248</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.1236</v>
+        <v>0.1317</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.139</v>
+        <v>0.1472</v>
       </c>
     </row>
     <row r="14">
@@ -1306,16 +1306,16 @@
       </c>
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="11" t="n">
-        <v>0.09480000000000001</v>
+        <v>0.1812</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0992</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.2472</v>
+        <v>0.2634</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.139</v>
+        <v>0.1472</v>
       </c>
     </row>
     <row r="16">
@@ -1325,7 +1325,7 @@
       <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="11" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="17"/>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="22"/>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>2729.699788491532</v>
+        <v>2810.375128736922</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>2675.069603186024</v>
@@ -1438,16 +1438,16 @@
       </c>
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.0506</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.0365</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.1609</v>
+        <v>0.1952</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.2112</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="26">
@@ -1478,16 +1478,16 @@
       </c>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="11" t="n">
-        <v>0.2448</v>
+        <v>0.6072</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.0272</v>
+        <v>0.146</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.3218</v>
+        <v>0.3904</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.2112</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="28">
@@ -1497,7 +1497,7 @@
       <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr"/>
       <c r="F28" s="11" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="29"/>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>1.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="34"/>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>81355.65915655205</v>
+        <v>85306.53277827147</v>
       </c>
       <c r="C36" s="5" t="n">
         <v>78668.05665352475</v>
@@ -1610,16 +1610,16 @@
       </c>
       <c r="B37" s="3" t="n"/>
       <c r="C37" s="10" t="n">
-        <v>0.0342</v>
+        <v>0.08439999999999999</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.0331</v>
+        <v>0.0833</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.204</v>
+        <v>0.2625</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0.321</v>
+        <v>0.3851</v>
       </c>
     </row>
     <row r="38">
@@ -1650,16 +1650,16 @@
       </c>
       <c r="B39" s="3" t="n"/>
       <c r="C39" s="11" t="n">
-        <v>0.4104</v>
+        <v>1.0128</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.1324</v>
+        <v>0.3332</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.408</v>
+        <v>0.525</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.321</v>
+        <v>0.3851</v>
       </c>
     </row>
     <row r="40">
@@ -1669,7 +1669,7 @@
       <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="3" t="inlineStr"/>
       <c r="F40" s="11" t="n">
-        <v>1.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="41"/>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="46"/>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>144441.0064047547</v>
+        <v>144574.8619031738</v>
       </c>
       <c r="C48" s="5" t="n">
         <v>143618.4502645293</v>
@@ -1782,16 +1782,16 @@
       </c>
       <c r="B49" s="3" t="n"/>
       <c r="C49" s="10" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0067</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.0098</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>0.0525</v>
+        <v>0.0535</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>0.0287</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="50">
@@ -1822,16 +1822,16 @@
       </c>
       <c r="B51" s="3" t="n"/>
       <c r="C51" s="11" t="n">
-        <v>0.0684</v>
+        <v>0.08040000000000001</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.0356</v>
+        <v>0.0392</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.0287</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="52">
@@ -1841,7 +1841,7 @@
       <c r="D52" s="3" t="inlineStr"/>
       <c r="E52" s="3" t="inlineStr"/>
       <c r="F52" s="11" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="53"/>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="59"/>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>159355.2532565184</v>
+        <v>160070.6928998046</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>158443.3101767823</v>
@@ -1961,16 +1961,16 @@
       </c>
       <c r="B62" s="3" t="n"/>
       <c r="C62" s="10" t="n">
-        <v>0.0058</v>
+        <v>0.0103</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.0061</v>
+        <v>0.0106</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>0.0496</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>0.0286</v>
+        <v>0.0332</v>
       </c>
     </row>
     <row r="63">
@@ -2001,16 +2001,16 @@
       </c>
       <c r="B64" s="3" t="n"/>
       <c r="C64" s="11" t="n">
-        <v>0.0696</v>
+        <v>0.1236</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>0.0244</v>
+        <v>0.0424</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.0992</v>
+        <v>0.1086</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>0.0286</v>
+        <v>0.0332</v>
       </c>
     </row>
     <row r="65">
@@ -2020,7 +2020,7 @@
       <c r="D65" s="3" t="inlineStr"/>
       <c r="E65" s="3" t="inlineStr"/>
       <c r="F65" s="11" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="66"/>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="71"/>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>138987.4048265014</v>
+        <v>138567.1508723143</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>138269.4341525026</v>
@@ -2133,16 +2133,16 @@
       </c>
       <c r="B74" s="3" t="n"/>
       <c r="C74" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0022</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>0.0525</v>
+        <v>0.0493</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>0.0364</v>
+        <v>0.0333</v>
       </c>
     </row>
     <row r="75">
@@ -2173,16 +2173,16 @@
       </c>
       <c r="B76" s="3" t="n"/>
       <c r="C76" s="11" t="n">
-        <v>0.0624</v>
+        <v>0.0264</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>0.0312</v>
+        <v>0.0188</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>0.105</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>0.0364</v>
+        <v>0.0333</v>
       </c>
     </row>
     <row r="77">
@@ -2192,7 +2192,7 @@
       <c r="D77" s="3" t="inlineStr"/>
       <c r="E77" s="3" t="inlineStr"/>
       <c r="F77" s="11" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="78"/>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="83"/>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>119863.6160416137</v>
+        <v>119634.2119427733</v>
       </c>
       <c r="C85" s="5" t="n">
         <v>119087.7085919464</v>
@@ -2305,16 +2305,16 @@
       </c>
       <c r="B86" s="3" t="n"/>
       <c r="C86" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0046</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.0144</v>
+        <v>0.0124</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>0.0104</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -2345,16 +2345,16 @@
       </c>
       <c r="B88" s="3" t="n"/>
       <c r="C88" s="11" t="n">
-        <v>0.07800000000000001</v>
+        <v>0.05520000000000001</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>0.0576</v>
+        <v>0.0496</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>0.08779999999999999</v>
+        <v>0.08380000000000001</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>0.0104</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -2364,7 +2364,7 @@
       <c r="D89" s="3" t="inlineStr"/>
       <c r="E89" s="3" t="inlineStr"/>
       <c r="F89" s="11" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
